--- a/~carmi/q1_mamad.xlsx
+++ b/~carmi/q1_mamad.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailmtaac-my.sharepoint.com/personal/carmi_mta_ac_il/Documents/CarmiMerimovich/www2/~carmi/ממד/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailmtaac-my.sharepoint.com/personal/carmi_mta_ac_il/Documents/CarmiMerimovich/www2/~carmi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="247" documentId="11_F25DC773A252ABDACC1048AD695E5DDC5BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1B88A34-0A1E-4740-BB90-E1A11904EB59}"/>
+  <xr:revisionPtr revIDLastSave="252" documentId="11_F25DC773A252ABDACC1048AD695E5DDC5BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83E53331-2AC0-448C-A3B3-B0DF94780417}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,9 +44,6 @@
     <t>אפשר לשנות דעה באופן חופשי</t>
   </si>
   <si>
-    <t>ü</t>
-  </si>
-  <si>
     <t>רוצה ממ"ד</t>
   </si>
   <si>
@@ -57,6 +54,9 @@
   </si>
   <si>
     <t>התשובות אינן מחייבות</t>
+  </si>
+  <si>
+    <t>V</t>
   </si>
 </sst>
 </file>
@@ -90,8 +90,8 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Wingdings"/>
-      <charset val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -185,14 +185,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -209,6 +209,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -509,7 +513,7 @@
   <sheetData>
     <row r="1" spans="1:32" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -615,8 +619,8 @@
       </c>
     </row>
     <row r="8" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
-        <v>3</v>
+      <c r="A8" s="8" t="s">
+        <v>2</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -632,8 +636,8 @@
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
-      <c r="P8" s="8" t="s">
-        <v>2</v>
+      <c r="P8" s="10" t="s">
+        <v>6</v>
       </c>
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
@@ -656,8 +660,8 @@
       </c>
     </row>
     <row r="9" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="10" t="s">
-        <v>5</v>
+      <c r="A9" s="9" t="s">
+        <v>4</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -695,8 +699,8 @@
       </c>
     </row>
     <row r="10" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
-        <v>4</v>
+      <c r="A10" s="8" t="s">
+        <v>3</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>

--- a/~carmi/q1_mamad.xlsx
+++ b/~carmi/q1_mamad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailmtaac-my.sharepoint.com/personal/carmi_mta_ac_il/Documents/CarmiMerimovich/www2/~carmi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="252" documentId="11_F25DC773A252ABDACC1048AD695E5DDC5BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83E53331-2AC0-448C-A3B3-B0DF94780417}"/>
+  <xr:revisionPtr revIDLastSave="270" documentId="11_F25DC773A252ABDACC1048AD695E5DDC5BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A5BAA84-19EF-48EE-9190-70E97C20E600}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
     <t>הן נועדו כדי לנסות להגיע לקונצנזוס</t>
   </si>
@@ -47,9 +47,6 @@
     <t>רוצה ממ"ד</t>
   </si>
   <si>
-    <t>לא רוצה ממד</t>
-  </si>
-  <si>
     <t>מה שהרוב יבחר</t>
   </si>
   <si>
@@ -57,13 +54,22 @@
   </si>
   <si>
     <t>V</t>
+  </si>
+  <si>
+    <t>עידכון הטבלה מתבצע על-ידי הודעה ציבורית או פרטית אלי</t>
+  </si>
+  <si>
+    <t>אם יש מספיק שמעוניינים בממ"ד, אז נדון באילוצים השונים</t>
+  </si>
+  <si>
+    <t>לא רוצה ממ"ד</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,27 +94,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -133,7 +143,9 @@
         <color auto="1"/>
       </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -146,17 +158,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -166,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -176,23 +177,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -209,10 +203,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -478,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.26953125" customWidth="1"/>
@@ -513,7 +503,7 @@
   <sheetData>
     <row r="1" spans="1:32" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -526,214 +516,228 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="4">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" ht="21" x14ac:dyDescent="0.5">
+      <c r="A6" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C8" s="4">
         <v>2</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D8" s="4">
         <v>3</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E8" s="4">
         <v>4</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F8" s="4">
         <v>5</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G8" s="4">
         <v>6</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H8" s="4">
         <v>7</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I8" s="4">
         <v>8</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J8" s="4">
         <v>9</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K8" s="4">
         <v>10</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L8" s="4">
         <v>11</v>
       </c>
-      <c r="M7" s="4">
+      <c r="M8" s="4">
         <v>12</v>
       </c>
-      <c r="N7" s="4">
+      <c r="N8" s="4">
         <v>13</v>
       </c>
-      <c r="O7" s="4">
+      <c r="O8" s="4">
         <v>14</v>
       </c>
-      <c r="P7" s="4">
+      <c r="P8" s="4">
         <v>15</v>
       </c>
-      <c r="Q7" s="4">
+      <c r="Q8" s="4">
         <v>16</v>
       </c>
-      <c r="R7" s="4">
+      <c r="R8" s="4">
         <v>17</v>
       </c>
-      <c r="S7" s="4">
+      <c r="S8" s="4">
         <v>18</v>
       </c>
-      <c r="T7" s="4">
+      <c r="T8" s="4">
         <v>19</v>
       </c>
-      <c r="U7" s="4">
+      <c r="U8" s="4">
         <v>20</v>
       </c>
-      <c r="V7" s="4">
+      <c r="V8" s="4">
         <v>21</v>
       </c>
-      <c r="W7" s="4">
+      <c r="W8" s="4">
         <v>22</v>
       </c>
-      <c r="X7" s="4">
+      <c r="X8" s="4">
         <v>23</v>
       </c>
-      <c r="Y7" s="4">
+      <c r="Y8" s="4">
         <v>24</v>
       </c>
-      <c r="Z7" s="4">
+      <c r="Z8" s="4">
         <v>25</v>
       </c>
-      <c r="AA7" s="4">
+      <c r="AA8" s="4">
         <v>26</v>
       </c>
-      <c r="AB7" s="4">
+      <c r="AB8" s="4">
         <v>27</v>
       </c>
-      <c r="AC7" s="4">
+      <c r="AC8" s="4">
         <v>28</v>
       </c>
-      <c r="AD7" s="4">
+      <c r="AD8" s="4">
         <v>29</v>
       </c>
-      <c r="AE7" s="4">
+      <c r="AE8" s="4">
         <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="6"/>
-      <c r="AA8" s="6"/>
-      <c r="AB8" s="6"/>
-      <c r="AC8" s="6"/>
-      <c r="AD8" s="6"/>
-      <c r="AE8" s="6"/>
-      <c r="AF8" s="6">
-        <f>COUNTA(B8:AE8)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-      <c r="T9" s="5"/>
-      <c r="U9" s="5"/>
-      <c r="V9" s="5"/>
-      <c r="W9" s="5"/>
-      <c r="X9" s="5"/>
-      <c r="Y9" s="5"/>
-      <c r="Z9" s="5"/>
-      <c r="AA9" s="5"/>
-      <c r="AB9" s="5"/>
-      <c r="AC9" s="5"/>
-      <c r="AD9" s="5"/>
-      <c r="AE9" s="5"/>
-      <c r="AF9" s="5">
+        <v>2</v>
+      </c>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="8"/>
+      <c r="AA9" s="8"/>
+      <c r="AB9" s="8"/>
+      <c r="AC9" s="8"/>
+      <c r="AD9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="8"/>
+      <c r="AF9" s="8">
         <f>COUNTA(B9:AE9)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="8"/>
+      <c r="AA10" s="8"/>
+      <c r="AB10" s="8"/>
+      <c r="AC10" s="8"/>
+      <c r="AD10" s="8"/>
+      <c r="AE10" s="8"/>
+      <c r="AF10" s="8">
+        <f>COUNTA(B10:AE10)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7"/>
-      <c r="Z10" s="7"/>
-      <c r="AA10" s="7"/>
-      <c r="AB10" s="7"/>
-      <c r="AC10" s="7"/>
-      <c r="AD10" s="7"/>
-      <c r="AE10" s="7"/>
-      <c r="AF10" s="7">
-        <f>COUNTA(B10:AE10)</f>
+    <row r="11" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="5"/>
+      <c r="AA11" s="5"/>
+      <c r="AB11" s="5"/>
+      <c r="AC11" s="5"/>
+      <c r="AD11" s="5"/>
+      <c r="AE11" s="5"/>
+      <c r="AF11" s="5">
+        <f>COUNTA(B11:AE11)</f>
         <v>0</v>
       </c>
     </row>

--- a/~carmi/q1_mamad.xlsx
+++ b/~carmi/q1_mamad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailmtaac-my.sharepoint.com/personal/carmi_mta_ac_il/Documents/CarmiMerimovich/www2/~carmi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="270" documentId="11_F25DC773A252ABDACC1048AD695E5DDC5BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A5BAA84-19EF-48EE-9190-70E97C20E600}"/>
+  <xr:revisionPtr revIDLastSave="274" documentId="11_F25DC773A252ABDACC1048AD695E5DDC5BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16104E77-DF53-4F6E-B0B4-304CF851D2B6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>הן נועדו כדי לנסות להגיע לקונצנזוס</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>לא רוצה ממ"ד</t>
+  </si>
+  <si>
+    <t>אני מדגיש. השאלה פה היא אם עקרונית יש רצון בממ"ד. לא משנה כרגע איפה, עם/בלי חדר, עם/בלי אמבטיה וכו'</t>
   </si>
 </sst>
 </file>
@@ -205,6 +208,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -468,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF11"/>
+  <dimension ref="A1:AF13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.26953125" customWidth="1"/>
@@ -521,223 +528,231 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:32" ht="21" x14ac:dyDescent="0.5">
-      <c r="A6" s="6" t="s">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A5" s="7"/>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" ht="21" x14ac:dyDescent="0.5">
+      <c r="A8" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="4">
+    <row r="10" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="4">
         <v>1</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C10" s="4">
         <v>2</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D10" s="4">
         <v>3</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E10" s="4">
         <v>4</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F10" s="4">
         <v>5</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G10" s="4">
         <v>6</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H10" s="4">
         <v>7</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I10" s="4">
         <v>8</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J10" s="4">
         <v>9</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K10" s="4">
         <v>10</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L10" s="4">
         <v>11</v>
       </c>
-      <c r="M8" s="4">
+      <c r="M10" s="4">
         <v>12</v>
       </c>
-      <c r="N8" s="4">
+      <c r="N10" s="4">
         <v>13</v>
       </c>
-      <c r="O8" s="4">
+      <c r="O10" s="4">
         <v>14</v>
       </c>
-      <c r="P8" s="4">
+      <c r="P10" s="4">
         <v>15</v>
       </c>
-      <c r="Q8" s="4">
+      <c r="Q10" s="4">
         <v>16</v>
       </c>
-      <c r="R8" s="4">
+      <c r="R10" s="4">
         <v>17</v>
       </c>
-      <c r="S8" s="4">
+      <c r="S10" s="4">
         <v>18</v>
       </c>
-      <c r="T8" s="4">
+      <c r="T10" s="4">
         <v>19</v>
       </c>
-      <c r="U8" s="4">
+      <c r="U10" s="4">
         <v>20</v>
       </c>
-      <c r="V8" s="4">
+      <c r="V10" s="4">
         <v>21</v>
       </c>
-      <c r="W8" s="4">
+      <c r="W10" s="4">
         <v>22</v>
       </c>
-      <c r="X8" s="4">
+      <c r="X10" s="4">
         <v>23</v>
       </c>
-      <c r="Y8" s="4">
+      <c r="Y10" s="4">
         <v>24</v>
       </c>
-      <c r="Z8" s="4">
+      <c r="Z10" s="4">
         <v>25</v>
       </c>
-      <c r="AA8" s="4">
+      <c r="AA10" s="4">
         <v>26</v>
       </c>
-      <c r="AB8" s="4">
+      <c r="AB10" s="4">
         <v>27</v>
       </c>
-      <c r="AC8" s="4">
+      <c r="AC10" s="4">
         <v>28</v>
       </c>
-      <c r="AD8" s="4">
+      <c r="AD10" s="4">
         <v>29</v>
       </c>
-      <c r="AE8" s="4">
+      <c r="AE10" s="4">
         <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-      <c r="W9" s="8"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="8"/>
-      <c r="Z9" s="8"/>
-      <c r="AA9" s="8"/>
-      <c r="AB9" s="8"/>
-      <c r="AC9" s="8"/>
-      <c r="AD9" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE9" s="8"/>
-      <c r="AF9" s="8">
-        <f>COUNTA(B9:AE9)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="8"/>
-      <c r="W10" s="8"/>
-      <c r="X10" s="8"/>
-      <c r="Y10" s="8"/>
-      <c r="Z10" s="8"/>
-      <c r="AA10" s="8"/>
-      <c r="AB10" s="8"/>
-      <c r="AC10" s="8"/>
-      <c r="AD10" s="8"/>
-      <c r="AE10" s="8"/>
-      <c r="AF10" s="8">
-        <f>COUNTA(B10:AE10)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="T11" s="8"/>
+      <c r="U11" s="8"/>
+      <c r="V11" s="8"/>
+      <c r="W11" s="8"/>
+      <c r="X11" s="8"/>
+      <c r="Y11" s="8"/>
+      <c r="Z11" s="8"/>
+      <c r="AA11" s="8"/>
+      <c r="AB11" s="8"/>
+      <c r="AC11" s="8"/>
+      <c r="AD11" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE11" s="8"/>
+      <c r="AF11" s="8">
+        <f>COUNTA(B11:AE11)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8"/>
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="8"/>
+      <c r="AA12" s="8"/>
+      <c r="AB12" s="8"/>
+      <c r="AC12" s="8"/>
+      <c r="AD12" s="8"/>
+      <c r="AE12" s="8"/>
+      <c r="AF12" s="8">
+        <f>COUNTA(B12:AE12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="5"/>
-      <c r="V11" s="5"/>
-      <c r="W11" s="5"/>
-      <c r="X11" s="5"/>
-      <c r="Y11" s="5"/>
-      <c r="Z11" s="5"/>
-      <c r="AA11" s="5"/>
-      <c r="AB11" s="5"/>
-      <c r="AC11" s="5"/>
-      <c r="AD11" s="5"/>
-      <c r="AE11" s="5"/>
-      <c r="AF11" s="5">
-        <f>COUNTA(B11:AE11)</f>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
+      <c r="Z13" s="5"/>
+      <c r="AA13" s="5"/>
+      <c r="AB13" s="5"/>
+      <c r="AC13" s="5"/>
+      <c r="AD13" s="5"/>
+      <c r="AE13" s="5"/>
+      <c r="AF13" s="5">
+        <f>COUNTA(B13:AE13)</f>
         <v>0</v>
       </c>
     </row>
